--- a/cleaned_pool.xlsx
+++ b/cleaned_pool.xlsx
@@ -878,7 +878,7 @@
         <v>26.66701815379319</v>
       </c>
       <c r="C13" t="n">
-        <v>4.34332507645327</v>
+        <v>4.343325076453271</v>
       </c>
       <c r="D13" t="n">
         <v>49.2063492063492</v>
@@ -5708,7 +5708,7 @@
         <v>1.996963771498219</v>
       </c>
       <c r="C151" t="n">
-        <v>25.00566689137635</v>
+        <v>25.00566689137636</v>
       </c>
       <c r="D151" t="n">
         <v>49.2063492063492</v>
@@ -5848,7 +5848,7 @@
         <v>2.043949330029355</v>
       </c>
       <c r="C155" t="n">
-        <v>25.5172107373879</v>
+        <v>25.51721073738789</v>
       </c>
       <c r="D155" t="n">
         <v>49.2063492063492</v>
@@ -6023,7 +6023,7 @@
         <v>2.136834972142061</v>
       </c>
       <c r="C160" t="n">
-        <v>28.37045368355803</v>
+        <v>28.37045368355804</v>
       </c>
       <c r="D160" t="n">
         <v>49.2063492063492</v>
@@ -6160,7 +6160,7 @@
         <v>39.99999999999999</v>
       </c>
       <c r="B164" t="n">
-        <v>2.056509825874311</v>
+        <v>2.056509825874312</v>
       </c>
       <c r="C164" t="n">
         <v>25.70043858692009</v>
@@ -6933,7 +6933,7 @@
         <v>0.015506784993774</v>
       </c>
       <c r="C186" t="n">
-        <v>26.0558062487381</v>
+        <v>26.05580624873809</v>
       </c>
       <c r="D186" t="n">
         <v>23.80952380952381</v>
@@ -7108,7 +7108,7 @@
         <v>0.0167473277932759</v>
       </c>
       <c r="C191" t="n">
-        <v>26.52307658432619</v>
+        <v>26.5230765843262</v>
       </c>
       <c r="D191" t="n">
         <v>23.80952380952381</v>
@@ -7843,7 +7843,7 @@
         <v>0.0010854749495642</v>
       </c>
       <c r="C212" t="n">
-        <v>25.91543641551279</v>
+        <v>25.9154364155128</v>
       </c>
       <c r="D212" t="n">
         <v>0</v>
@@ -8225,7 +8225,7 @@
         <v>39.99999999999999</v>
       </c>
       <c r="B223" t="n">
-        <v>23.04230716149851</v>
+        <v>23.04230716149852</v>
       </c>
       <c r="C223" t="n">
         <v>14.47352564000485</v>
@@ -9310,7 +9310,7 @@
         <v>39.99999999999999</v>
       </c>
       <c r="B254" t="n">
-        <v>22.98880875326999</v>
+        <v>22.98880875327</v>
       </c>
       <c r="C254" t="n">
         <v>14.15448899384515</v>
@@ -9415,7 +9415,7 @@
         <v>39.99999999999999</v>
       </c>
       <c r="B257" t="n">
-        <v>22.98446685347174</v>
+        <v>22.98446685347173</v>
       </c>
       <c r="C257" t="n">
         <v>13.88090543653937</v>
@@ -9485,7 +9485,7 @@
         <v>39.99999999999999</v>
       </c>
       <c r="B259" t="n">
-        <v>22.98167563217286</v>
+        <v>22.98167563217285</v>
       </c>
       <c r="C259" t="n">
         <v>12.54035386959721</v>
@@ -9835,7 +9835,7 @@
         <v>39.99999999999999</v>
       </c>
       <c r="B269" t="n">
-        <v>22.95453875843375</v>
+        <v>22.95453875843376</v>
       </c>
       <c r="C269" t="n">
         <v>12.40847700107126</v>
@@ -13405,7 +13405,7 @@
         <v>39.99999999999999</v>
       </c>
       <c r="B371" t="n">
-        <v>2.263215269841319</v>
+        <v>2.26321526984132</v>
       </c>
       <c r="C371" t="n">
         <v>23.72448743876759</v>
@@ -15333,7 +15333,7 @@
         <v>14.06418878580323</v>
       </c>
       <c r="C426" t="n">
-        <v>28.79007519419302</v>
+        <v>28.79007519419301</v>
       </c>
       <c r="D426" t="n">
         <v>100</v>
@@ -15753,7 +15753,7 @@
         <v>13.92307704235988</v>
       </c>
       <c r="C438" t="n">
-        <v>29.12605537865155</v>
+        <v>29.12605537865156</v>
       </c>
       <c r="D438" t="n">
         <v>49.2063492063492</v>
@@ -16628,7 +16628,7 @@
         <v>13.56502537685364</v>
       </c>
       <c r="C463" t="n">
-        <v>31.42991950065299</v>
+        <v>31.429919500653</v>
       </c>
       <c r="D463" t="n">
         <v>23.80952380952381</v>
@@ -16663,7 +16663,7 @@
         <v>13.56440510545389</v>
       </c>
       <c r="C464" t="n">
-        <v>31.42991950065299</v>
+        <v>31.429919500653</v>
       </c>
       <c r="D464" t="n">
         <v>49.2063492063492</v>
@@ -16908,7 +16908,7 @@
         <v>13.56285442695452</v>
       </c>
       <c r="C471" t="n">
-        <v>31.42991950065299</v>
+        <v>31.429919500653</v>
       </c>
       <c r="D471" t="n">
         <v>100</v>
@@ -17083,7 +17083,7 @@
         <v>13.55959800210582</v>
       </c>
       <c r="C476" t="n">
-        <v>31.42991950065299</v>
+        <v>31.429919500653</v>
       </c>
       <c r="D476" t="n">
         <v>100</v>
@@ -17223,7 +17223,7 @@
         <v>13.56052840920545</v>
       </c>
       <c r="C480" t="n">
-        <v>31.42991950065299</v>
+        <v>31.429919500653</v>
       </c>
       <c r="D480" t="n">
         <v>100</v>
@@ -17573,7 +17573,7 @@
         <v>14.19274003340162</v>
       </c>
       <c r="C490" t="n">
-        <v>27.6381431331923</v>
+        <v>27.63814313319229</v>
       </c>
       <c r="D490" t="n">
         <v>23.80952380952381</v>
@@ -17923,7 +17923,7 @@
         <v>14.19165455845205</v>
       </c>
       <c r="C500" t="n">
-        <v>30.22999027044391</v>
+        <v>30.22999027044392</v>
       </c>
       <c r="D500" t="n">
         <v>23.80952380952381</v>
@@ -18308,7 +18308,7 @@
         <v>14.20002822234869</v>
       </c>
       <c r="C511" t="n">
-        <v>36.70960811357295</v>
+        <v>36.70960811357296</v>
       </c>
       <c r="D511" t="n">
         <v>100</v>
@@ -18763,7 +18763,7 @@
         <v>14.17940419830697</v>
       </c>
       <c r="C524" t="n">
-        <v>24.99829882673231</v>
+        <v>24.99829882673232</v>
       </c>
       <c r="D524" t="n">
         <v>100</v>
@@ -19918,7 +19918,7 @@
         <v>14.10714258023598</v>
       </c>
       <c r="C557" t="n">
-        <v>29.12605537865155</v>
+        <v>29.12605537865156</v>
       </c>
       <c r="D557" t="n">
         <v>23.80952380952381</v>
@@ -20583,7 +20583,7 @@
         <v>14.09380674514134</v>
       </c>
       <c r="C576" t="n">
-        <v>30.22999027044391</v>
+        <v>30.22999027044392</v>
       </c>
       <c r="D576" t="n">
         <v>49.2063492063492</v>
@@ -21213,7 +21213,7 @@
         <v>14.07550873884868</v>
       </c>
       <c r="C594" t="n">
-        <v>31.42991950065299</v>
+        <v>31.429919500653</v>
       </c>
       <c r="D594" t="n">
         <v>23.80952380952381</v>
@@ -21318,7 +21318,7 @@
         <v>14.04666611876026</v>
       </c>
       <c r="C597" t="n">
-        <v>31.42991950065299</v>
+        <v>31.429919500653</v>
       </c>
       <c r="D597" t="n">
         <v>23.80952380952381</v>
@@ -21528,7 +21528,7 @@
         <v>14.01255119177396</v>
       </c>
       <c r="C603" t="n">
-        <v>38.48550337428239</v>
+        <v>38.4855033742824</v>
       </c>
       <c r="D603" t="n">
         <v>100</v>
@@ -24255,7 +24255,7 @@
         <v>39.99999999999999</v>
       </c>
       <c r="B681" t="n">
-        <v>22.59617695722763</v>
+        <v>22.59617695722764</v>
       </c>
       <c r="C681" t="n">
         <v>13.13030036195364</v>
@@ -24360,7 +24360,7 @@
         <v>39.99999999999999</v>
       </c>
       <c r="B684" t="n">
-        <v>22.5865627505315</v>
+        <v>22.58656275053149</v>
       </c>
       <c r="C684" t="n">
         <v>10.54081115283542</v>
@@ -24430,7 +24430,7 @@
         <v>39.99999999999999</v>
       </c>
       <c r="B686" t="n">
-        <v>22.58764822548106</v>
+        <v>22.58764822548105</v>
       </c>
       <c r="C686" t="n">
         <v>12.8809374817534</v>
@@ -24745,7 +24745,7 @@
         <v>39.99999999999999</v>
       </c>
       <c r="B695" t="n">
-        <v>22.5865627505315</v>
+        <v>22.58656275053149</v>
       </c>
       <c r="C695" t="n">
         <v>10.83271749509443</v>
@@ -24850,7 +24850,7 @@
         <v>39.99999999999999</v>
       </c>
       <c r="B698" t="n">
-        <v>22.57276171188703</v>
+        <v>22.57276171188704</v>
       </c>
       <c r="C698" t="n">
         <v>12.19631016071166</v>
@@ -25585,7 +25585,7 @@
         <v>39.99999999999999</v>
       </c>
       <c r="B719" t="n">
-        <v>22.54004239555018</v>
+        <v>22.54004239555017</v>
       </c>
       <c r="C719" t="n">
         <v>10.70139109650269</v>
@@ -25760,7 +25760,7 @@
         <v>39.99999999999999</v>
       </c>
       <c r="B724" t="n">
-        <v>22.53740624210123</v>
+        <v>22.53740624210124</v>
       </c>
       <c r="C724" t="n">
         <v>12.19568105221542</v>
